--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121101666</v>
+        <v>121101722</v>
       </c>
       <c r="B2" t="n">
-        <v>57501</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Simondal, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571023</v>
+        <v>570966</v>
       </c>
       <c r="R2" t="n">
-        <v>6422353</v>
+        <v>6422342</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat murket träd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121101722</v>
+        <v>121101639</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570966</v>
+        <v>571086</v>
       </c>
       <c r="R3" t="n">
-        <v>6422342</v>
+        <v>6422364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,17 +876,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat murket träd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121101639</v>
+        <v>121101666</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,49 +913,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 51590, Simondal, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571086</v>
+        <v>571023</v>
       </c>
       <c r="R4" t="n">
-        <v>6422364</v>
+        <v>6422353</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +997,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121101722</v>
+        <v>121101639</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570966</v>
+        <v>571086</v>
       </c>
       <c r="R2" t="n">
-        <v>6422342</v>
+        <v>6422364</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +761,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat murket träd</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121101639</v>
+        <v>121101722</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571086</v>
+        <v>570966</v>
       </c>
       <c r="R3" t="n">
-        <v>6422364</v>
+        <v>6422342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,13 +872,17 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat murket träd</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121101639</v>
+        <v>121101722</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571086</v>
+        <v>570966</v>
       </c>
       <c r="R2" t="n">
-        <v>6422364</v>
+        <v>6422342</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,13 +761,17 @@
           <t>2024-11-09</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat murket träd</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121101722</v>
+        <v>121101639</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570966</v>
+        <v>571086</v>
       </c>
       <c r="R3" t="n">
-        <v>6422342</v>
+        <v>6422364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +876,13 @@
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat murket träd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121101639</v>
+        <v>121101666</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,49 +802,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 51590, Simondal, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571086</v>
+        <v>571023</v>
       </c>
       <c r="R3" t="n">
-        <v>6422364</v>
+        <v>6422353</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121101666</v>
+        <v>121101639</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,53 +916,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Simondal, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571023</v>
+        <v>571086</v>
       </c>
       <c r="R4" t="n">
-        <v>6422353</v>
+        <v>6422364</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>121101639</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121101722</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121101666</v>
+        <v>121101639</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,53 +802,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 51590, Sm</t>
+          <t>A 51590, Simondal, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571023</v>
+        <v>571086</v>
       </c>
       <c r="R3" t="n">
-        <v>6422353</v>
+        <v>6422364</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,6 +882,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121101639</v>
+        <v>121101666</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,49 +913,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 51590, Simondal, Sm</t>
+          <t>A 51590, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571086</v>
+        <v>571023</v>
       </c>
       <c r="R4" t="n">
-        <v>6422364</v>
+        <v>6422353</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +997,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,442 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128984295</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 51590, Hafvet, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570987</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6422361</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128984395</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92140</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 51590, Hafvet, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571006</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6422330</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128984330</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91669</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 51590, Hafvet, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>570987</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6422352</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128984284</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57880</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 51590, Hafvet, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>570987</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6422361</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,45 +1233,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128984330</v>
+        <v>128984284</v>
       </c>
       <c r="B7" t="n">
-        <v>91669</v>
+        <v>57880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,7 +1283,7 @@
         <v>570987</v>
       </c>
       <c r="R7" t="n">
-        <v>6422352</v>
+        <v>6422361</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1323,7 +1324,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1339,115 +1339,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>128984284</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57880</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>A 51590, Hafvet, Sm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>570987</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6422361</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Odensvi</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>128984295</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>128984284</v>
       </c>
       <c r="B7" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>128984295</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>128984284</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>128984295</v>
       </c>
       <c r="B5" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>128984284</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,6 +1340,115 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129504756</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92202</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Simondal, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>570971</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6422340</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>128984395</v>
       </c>
       <c r="B6" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>129504756</v>
       </c>
       <c r="B8" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1345,7 +1345,7 @@
         <v>129504756</v>
       </c>
       <c r="B8" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1345,7 +1345,7 @@
         <v>129504756</v>
       </c>
       <c r="B8" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1345,7 +1345,7 @@
         <v>129504756</v>
       </c>
       <c r="B8" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1345,7 +1345,7 @@
         <v>129504756</v>
       </c>
       <c r="B8" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1345,7 +1345,7 @@
         <v>129504756</v>
       </c>
       <c r="B8" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1345,7 +1345,7 @@
         <v>129504756</v>
       </c>
       <c r="B8" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 51590-2024 artfynd.xlsx
+++ b/artfynd/A 51590-2024 artfynd.xlsx
@@ -1345,7 +1345,7 @@
         <v>129504756</v>
       </c>
       <c r="B8" t="n">
-        <v>92250</v>
+        <v>92252</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
